--- a/docs/Requirements/Scope Baseline.xlsx
+++ b/docs/Requirements/Scope Baseline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c906530d9ff38bc/Desktop/SEN381/Ticketing-System/docs/Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A97EEBFC-150E-4EB3-B19B-67290A17D8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{A97EEBFC-150E-4EB3-B19B-67290A17D8A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D54948A-4743-41B4-94C4-29F13F3F7936}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{692520EF-F46F-4B4C-9EE5-ED1995D560B8}"/>
+    <workbookView xWindow="9228" yWindow="0" windowWidth="21588" windowHeight="17376" xr2:uid="{692520EF-F46F-4B4C-9EE5-ED1995D560B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Scope Baseline" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="102">
   <si>
     <t>Scope Baseline</t>
   </si>
@@ -324,13 +324,34 @@
   </si>
   <si>
     <t>Total items</t>
+  </si>
+  <si>
+    <t>SCP-021</t>
+  </si>
+  <si>
+    <t>Project charter, work breakdown structure and project timeline</t>
+  </si>
+  <si>
+    <t>Directed by the client (lecturer) on 09/09/2026. The WBS also supplies the activity decomposition that the PERT estimation in CON-009 requires, so it is a dependency of the effort estimate rather than only a planning document.</t>
+  </si>
+  <si>
+    <t>Lecturer instruction, verbal, 09/09/2026; CON-009</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>PRODUCT</t>
+  </si>
+  <si>
+    <t>PROJECT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -400,8 +421,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.5"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -423,6 +466,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCDE7F3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -480,8 +535,56 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -491,59 +594,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -932,517 +996,606 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09AEAD61-01CF-4EE9-97DC-EF3173C077C3}">
-  <dimension ref="B1:K30"/>
+  <dimension ref="B1:L30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.21875" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="39.77734375" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" customWidth="1"/>
-    <col min="5" max="5" width="63" customWidth="1"/>
-    <col min="6" max="6" width="27.77734375" customWidth="1"/>
-    <col min="7" max="7" width="17.5546875" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" customWidth="1"/>
-    <col min="11" max="11" width="29.21875" customWidth="1"/>
+    <col min="2" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="39.77734375" customWidth="1"/>
+    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="6" max="6" width="63" customWidth="1"/>
+    <col min="7" max="7" width="27.77734375" customWidth="1"/>
+    <col min="8" max="8" width="17.5546875" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="29.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
+    <row r="1" spans="2:12" ht="25.8" x14ac:dyDescent="0.3">
+      <c r="B1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="3" t="s">
+      <c r="C1" s="17"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+    </row>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="4" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B4" s="4" t="s">
+      <c r="C2" s="19"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+    </row>
+    <row r="4" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="H4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="K4" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="K4" s="17"/>
-    </row>
-    <row r="5" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B5" s="6" t="s">
+      <c r="L4" s="21"/>
+    </row>
+    <row r="5" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J5" s="18" t="s">
+      <c r="H5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K5" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="K5" s="19">
-        <f>COUNTIF($D$5:$D$24,"IN SCOPE")</f>
+      <c r="L5" s="14">
+        <f>COUNTIF($E$5:$E$25,"IN SCOPE")</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B6" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="L6" s="14">
+        <f>COUNTIF($E$5:$E$25,"DEFERRED")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="13" t="s">
+      <c r="H7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="L7" s="14">
+        <f>COUNTIF($E$5:$E$25,"OUT OF SCOPE")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J6" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="K6" s="19">
-        <f>COUNTIF($D$5:$D$24,"DEFERRED")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="F8" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="L8" s="16">
+        <f>COUNTA($B$5:$B$25)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="K7" s="19">
-        <f>COUNTIF($D$5:$D$24,"OUT OF SCOPE")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="13" t="s">
+      <c r="F9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J8" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="K8" s="21">
-        <f>COUNTA($B$5:$B$24)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="F10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="13" t="s">
+      <c r="F11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="8" t="s">
+      <c r="F12" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="13" t="s">
+      <c r="F13" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="8" t="s">
+      <c r="F14" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="13" t="s">
+      <c r="F15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B16" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="G14" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="8" t="s">
+      <c r="F16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="H16" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B18" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B20" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B22" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B23" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B24" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B25" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B16" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B18" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G18" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B19" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B20" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="G20" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B21" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B22" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="G22" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B23" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="G24" s="15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="2:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="2:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="30" spans="2:7" ht="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="F25" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="2:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="K4:L4"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5:D24">
+  <phoneticPr fontId="9" type="noConversion"/>
+  <conditionalFormatting sqref="E5:E25">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="OUT OF SCOPE">
-      <formula>NOT(ISERROR(SEARCH("OUT OF SCOPE",D5)))</formula>
+      <formula>NOT(ISERROR(SEARCH("OUT OF SCOPE",E5)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="IN SCOPE">
-      <formula>NOT(ISERROR(SEARCH("IN SCOPE",D5)))</formula>
+      <formula>NOT(ISERROR(SEARCH("IN SCOPE",E5)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="DEFERRED">
-      <formula>NOT(ISERROR(SEARCH("DEFERRED",D5)))</formula>
+      <formula>NOT(ISERROR(SEARCH("DEFERRED",E5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G24">
+  <conditionalFormatting sqref="H5:H25">
     <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",G5)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Yes",H5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
